--- a/data/teams_data.xlsx
+++ b/data/teams_data.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Github\Egyptian-Premier-League-Schedule-Optimizer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ibram\OneDrive\Documents\GitHub\Egyptian-Premier-League-Schedule-Optimizer\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7858B7-7D69-49A4-A99C-DB89A9EDDCB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3981F02-CAF5-4263-BE57-5F7F98FF1CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5370" yWindow="3300" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2425 Season Team Data Strategy" sheetId="1" r:id="rId1"/>
+    <sheet name="Teams" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -396,20 +396,6 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
         <strike val="0"/>
         <outline val="0"/>
@@ -425,9 +411,47 @@
     </dxf>
     <dxf>
       <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <family val="2"/>
       </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <border>
@@ -445,37 +469,13 @@
         </bottom>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF356854"/>
-          <bgColor rgb="FF356854"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="2425 Season Team Data Strategy-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="9"/>
-      <tableStyleElement type="headerRow" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="secondRowStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="12"/>
+      <tableStyleElement type="headerRow" dxfId="11"/>
+      <tableStyleElement type="firstRowStripe" dxfId="10"/>
+      <tableStyleElement type="secondRowStripe" dxfId="9"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -490,15 +490,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Season_Team_Details" displayName="Season_Team_Details" ref="A1:G19" headerRowDxfId="8" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Season_Team_Details" displayName="Season_Team_Details" ref="A1:G19" headerRowDxfId="8" dataDxfId="7">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Team_ID" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Team_Name" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Home_Stadium" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Alt_Stadium" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tier" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Gov_ID" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Cont_Flag" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Team_ID" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Team_Name" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Home_Stadium" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Alt_Stadium" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tier" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Gov_ID" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Cont_Flag" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="2425 Season Team Data Strategy-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -706,15 +706,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" style="2"/>
-    <col min="2" max="3" width="16.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="2"/>
+    <col min="2" max="3" width="16.88671875" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="7" max="7" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" s="2" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -737,7 +737,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -760,7 +760,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
@@ -783,7 +783,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
@@ -806,7 +806,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>21</v>
       </c>
@@ -829,7 +829,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>24</v>
       </c>
@@ -852,7 +852,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>27</v>
       </c>
@@ -875,7 +875,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>31</v>
       </c>
@@ -898,7 +898,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>33</v>
       </c>
@@ -921,7 +921,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>36</v>
       </c>
@@ -944,7 +944,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
@@ -967,7 +967,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>40</v>
       </c>
@@ -990,7 +990,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>44</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>46</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>48</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>52</v>
       </c>
@@ -1082,7 +1082,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>56</v>
       </c>
@@ -1105,7 +1105,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>61</v>
       </c>
@@ -1128,7 +1128,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>65</v>
       </c>
